--- a/artfynd/A 61363-2022 artfynd.xlsx
+++ b/artfynd/A 61363-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61363-2022 artfynd.xlsx
+++ b/artfynd/A 61363-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104501953</v>
+        <v>123545803</v>
       </c>
       <c r="B2" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dalsätra, Upl</t>
+          <t>Dalsätra, Dalsätra, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>693403.9275380716</v>
+        <v>693243</v>
       </c>
       <c r="R2" t="n">
-        <v>6604031.339444269</v>
+        <v>6603882</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-06</t>
+          <t>2025-03-28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,45 +783,36 @@
           <t>Tomas Fridström</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Nya Tärnan gruppen</t>
-        </is>
-      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104502090</v>
+        <v>104501953</v>
       </c>
       <c r="B3" t="n">
-        <v>77595</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6450</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>693390.2075890506</v>
+        <v>693404</v>
       </c>
       <c r="R3" t="n">
-        <v>6604020.977393213</v>
+        <v>6604031</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -902,6 +892,118 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Nya Tärnan gruppen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104502090</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalsätra, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>693391</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6604022</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Fridström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Nya Tärnan gruppen</t>
         </is>

--- a/artfynd/A 61363-2022 artfynd.xlsx
+++ b/artfynd/A 61363-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104501953</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>Nya Tärnan gruppen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104502090</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,8 +1023,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123545803</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>